--- a/data/trans_dic/IP2005-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen los dientes sanos</t>
+          <t>Menores que tienen los dientes sanos (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,78; 97,15</t>
+          <t>83,56; 97,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,14; 94,15</t>
+          <t>78,39; 94,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,89; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92,21; 99,34</t>
+          <t>92,25; 99,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,18; 94,52</t>
+          <t>80,4; 94,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,33; 95,39</t>
+          <t>81,93; 95,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,17; 99,02</t>
+          <t>88,76; 99,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>93,18; 99,25</t>
+          <t>92,86; 99,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84,73; 94,5</t>
+          <t>84,58; 94,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83,24; 93,1</t>
+          <t>83,72; 93,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93,87; 99,5</t>
+          <t>93,87; 99,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,62; 98,86</t>
+          <t>94,39; 98,77</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,31; 88,99</t>
+          <t>76,97; 89,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,68; 93,87</t>
+          <t>83,12; 93,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92,85; 99,29</t>
+          <t>93,24; 99,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,6; 93,79</t>
+          <t>79,59; 93,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,96; 88,14</t>
+          <t>76,34; 87,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,92; 91,87</t>
+          <t>80,51; 92,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,85; 93,79</t>
+          <t>83,0; 93,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,84; 86,49</t>
+          <t>71,56; 86,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78,25; 86,83</t>
+          <t>78,38; 86,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84,13; 91,9</t>
+          <t>84,25; 91,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89,59; 95,57</t>
+          <t>89,63; 95,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,76; 88,87</t>
+          <t>78,32; 89,08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92,39; 98,94</t>
+          <t>91,34; 98,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,57; 96,62</t>
+          <t>85,55; 96,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,52; 98,76</t>
+          <t>89,41; 98,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78,42; 93,28</t>
+          <t>78,27; 93,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>90,66; 99,05</t>
+          <t>91,44; 99,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,65; 99,03</t>
+          <t>90,78; 99,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,8; 98,92</t>
+          <t>89,81; 98,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76,83; 91,45</t>
+          <t>76,72; 91,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93,41; 98,51</t>
+          <t>93,18; 98,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90,72; 97,44</t>
+          <t>90,92; 97,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92,37; 98,69</t>
+          <t>92,24; 98,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80,66; 90,63</t>
+          <t>80,54; 90,77</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,26; 97,83</t>
+          <t>90,39; 98,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,67; 92,77</t>
+          <t>79,15; 91,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,08; 95,06</t>
+          <t>83,32; 95,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,91; 80,03</t>
+          <t>61,63; 80,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,33; 99,07</t>
+          <t>90,9; 98,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,63; 94,25</t>
+          <t>82,46; 94,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,15; 92,09</t>
+          <t>78,63; 91,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,16; 90,2</t>
+          <t>70,39; 90,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,79; 97,91</t>
+          <t>92,73; 97,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83,45; 91,9</t>
+          <t>82,18; 91,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83,31; 92,57</t>
+          <t>83,98; 92,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,37; 84,33</t>
+          <t>69,26; 83,95</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>69,5; 90,69</t>
+          <t>70,45; 90,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75,57; 94,27</t>
+          <t>74,03; 94,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,82; 95,0</t>
+          <t>77,52; 95,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84,9; 97,75</t>
+          <t>85,98; 97,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>72,11; 91,56</t>
+          <t>71,11; 90,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,91; 95,18</t>
+          <t>79,56; 94,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,81; 88,29</t>
+          <t>68,08; 88,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,97; 97,06</t>
+          <t>84,16; 97,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>74,33; 88,51</t>
+          <t>74,38; 88,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80,97; 93,09</t>
+          <t>79,71; 92,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76,48; 89,53</t>
+          <t>76,59; 89,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,45; 96,46</t>
+          <t>88,04; 96,31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,52 +1417,52 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86,52; 97,52</t>
+          <t>87,29; 97,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84,84; 98,07</t>
+          <t>85,51; 97,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83,75; 98,46</t>
+          <t>84,84; 98,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81,84; 95,96</t>
+          <t>81,59; 95,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92,35; 100,0</t>
+          <t>92,61; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,65; 90,86</t>
+          <t>73,25; 90,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>97,34; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89,55; 98,97</t>
+          <t>89,96; 98,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91,71; 98,2</t>
+          <t>92,12; 98,29</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>82,42; 92,94</t>
+          <t>81,74; 93,22</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,14 +1472,14 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>88,52; 97,04</t>
+          <t>88,58; 96,69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>83,8; 93,03</t>
+          <t>83,86; 93,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,84; 95,29</t>
+          <t>86,79; 95,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91,28; 97,88</t>
+          <t>91,51; 97,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78,67; 89,67</t>
+          <t>79,34; 89,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,91; 93,53</t>
+          <t>84,73; 93,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,79; 97,17</t>
+          <t>89,96; 97,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,05; 96,54</t>
+          <t>89,28; 96,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>74,78; 87,72</t>
+          <t>74,67; 87,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85,82; 92,21</t>
+          <t>85,82; 92,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90,19; 95,63</t>
+          <t>89,92; 95,66</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91,75; 96,4</t>
+          <t>91,55; 96,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,8; 86,8</t>
+          <t>78,31; 87,15</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>79,37; 88,81</t>
+          <t>79,2; 88,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,6; 94,06</t>
+          <t>87,09; 94,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83,42; 91,73</t>
+          <t>83,14; 91,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87,52; 95,69</t>
+          <t>87,17; 95,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>77,85; 88,19</t>
+          <t>78,13; 87,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,79; 94,49</t>
+          <t>88,0; 94,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,53; 92,49</t>
+          <t>84,2; 92,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>93,57; 98,75</t>
+          <t>93,4; 98,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>80,33; 86,89</t>
+          <t>80,35; 87,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88,91; 93,75</t>
+          <t>88,64; 93,57</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85,35; 91,18</t>
+          <t>84,42; 90,92</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>91,85; 96,6</t>
+          <t>91,91; 96,4</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>86,8; 90,72</t>
+          <t>86,87; 90,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>88,31; 92,24</t>
+          <t>88,19; 92,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91,3; 94,61</t>
+          <t>91,45; 94,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85,27; 89,93</t>
+          <t>85,5; 90,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>86,69; 90,79</t>
+          <t>86,73; 90,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>88,86; 92,5</t>
+          <t>88,92; 92,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89,35; 92,87</t>
+          <t>89,16; 92,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>85,67; 90,08</t>
+          <t>85,44; 90,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>87,59; 90,24</t>
+          <t>87,41; 90,12</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>89,25; 91,75</t>
+          <t>89,17; 91,91</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>90,9; 93,33</t>
+          <t>90,94; 93,48</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>86,23; 89,35</t>
+          <t>86,17; 89,43</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen los dientes sanos (tasa de respuesta: 99,37%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>43204</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48010</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55501</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>71009</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46827</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>52915</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>58497</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>74770</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>90030</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>100925</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>113998</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>145778</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>39281; 45677</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42680; 51333</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>67212; 72370</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>42219; 49730</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>48140; 55968</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>54144; 60408</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>71509; 76432</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>84178; 94192</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>94769; 105604</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>109363; 115908</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>141465; 148030</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>78251</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86023</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>94018</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>109199</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87125</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88041</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93713</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>99330</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>165377</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>174064</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>187731</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>208528</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>72038; 83488</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>79774; 89990</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>90293; 96135</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>99971; 117083</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>80550; 92841</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>81036; 93220</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>87136; 98364</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>89209; 107628</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>156070; 172961</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>165660; 179854</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>180900; 193104</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>196019; 222938</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>61242</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>58230</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>58686</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>49671</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>62248</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64373</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>63657</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>55939</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>123490</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>122603</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>122342</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>105610</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>57797; 62612</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53725; 60840</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>54652; 60352</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>44453; 53052</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>59120; 64022</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>60297; 65777</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>59224; 65226</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>50302; 60298</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>119209; 125984</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>117484; 125625</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>117207; 125480</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>98539; 111067</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>67494</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62468</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>65739</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>50431</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73455</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69556</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>66725</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>61416</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>140949</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>132024</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>132464</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>111846</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>63867; 69608</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>57350; 66608</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>60623; 69246</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>42945; 55880</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>69405; 75539</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>64019; 73242</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>60637; 70847</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>53049; 67972</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>136327; 143822</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>123344; 137451</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>125862; 138768</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>100455; 121764</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>31777</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>35661</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>36198</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>31980</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34773</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>40280</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34038</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>37639</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>66550</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>75941</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>70235</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>69618</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>27126; 34960</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30460; 38792</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>31752; 38963</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>29404; 33389</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>29918; 38161</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>35997; 42947</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>28989; 37607</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>34269; 39611</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>59937; 71422</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>68865; 79953</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>63986; 75131</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>65957; 72151</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>50060</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>45904</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>47160</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>39581</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>55873</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>46541</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>53925</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>52128</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>105933</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>92444</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>101085</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>91709</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>46611; 52135</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>41961; 47857</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>42785; 49662</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>35830; 42067</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>52892; 57110</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>40746; 50568</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>48723; 53603</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>101799; 108616</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>85576; 97600</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>95934; 103594</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>86872; 94830</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>109111</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>117369</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>123784</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>104960</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>112895</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>123363</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>125172</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>126628</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>222006</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>240732</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>248956</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>231588</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>102725; 114131</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>110692; 121902</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>118808; 127129</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>98053; 111072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>106546; 117625</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>117471; 127315</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>119453; 129174</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>115625; 135035</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>213032; 229139</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>232092; 246905</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>241347; 253897</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>218035; 242652</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>123903</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>142823</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>130851</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>119720</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>129248</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>150906</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>140884</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>149242</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>253151</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>293729</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>271736</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>268963</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>116509; 130515</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>136627; 148055</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>123815; 136145</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>113214; 123662</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>120550; 135349</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>144923; 156036</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>133708; 146333</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>144219; 152160</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>242173; 263146</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>285026; 300888</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>259796; 279781</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>261288; 274067</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1749</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1771</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>1829</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1633</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>565042</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>596489</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>611937</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>576551</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>602445</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>635974</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>636612</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>657092</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1167487</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1232463</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1248548</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1233643</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>552531; 576424</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>582311; 608271</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>600248; 621850</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>561306; 591304</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>588262; 613949</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>622104; 647771</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>622476; 648463</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>638014; 673197</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1148769; 1184449</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>1212613; 1249917</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>1231855; 1266165</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1209241; 1254989</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2005-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Provincia-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,56; 97,16</t>
+          <t>83,62; 96,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,39; 94,29</t>
+          <t>78,04; 94,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92,25; 99,33</t>
+          <t>93,59; 99,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,4; 94,7</t>
+          <t>80,95; 94,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,93; 95,25</t>
+          <t>81,62; 94,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,76; 99,03</t>
+          <t>87,64; 99,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>92,86; 99,25</t>
+          <t>92,61; 99,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84,58; 94,64</t>
+          <t>84,94; 94,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83,72; 93,29</t>
+          <t>83,68; 93,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93,87; 99,49</t>
+          <t>94,23; 99,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,39; 98,77</t>
+          <t>94,13; 98,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,97; 89,2</t>
+          <t>76,67; 89,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,12; 93,77</t>
+          <t>83,55; 93,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,24; 99,27</t>
+          <t>92,35; 99,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,59; 93,21</t>
+          <t>80,08; 94,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>76,34; 87,99</t>
+          <t>76,06; 87,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,51; 92,62</t>
+          <t>81,01; 92,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,0; 93,69</t>
+          <t>82,69; 93,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,56; 86,33</t>
+          <t>71,2; 86,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78,38; 86,87</t>
+          <t>78,39; 86,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84,25; 91,47</t>
+          <t>84,3; 92,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89,63; 95,68</t>
+          <t>89,5; 95,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,32; 89,08</t>
+          <t>77,41; 88,96</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91,34; 98,94</t>
+          <t>91,32; 98,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,55; 96,88</t>
+          <t>84,98; 96,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,41; 98,74</t>
+          <t>89,31; 98,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78,27; 93,41</t>
+          <t>79,13; 93,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,44; 99,02</t>
+          <t>91,18; 99,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,78; 99,03</t>
+          <t>91,67; 99,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,81; 98,91</t>
+          <t>90,77; 98,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76,72; 91,97</t>
+          <t>75,1; 91,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93,18; 98,48</t>
+          <t>93,05; 98,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90,92; 97,22</t>
+          <t>90,62; 97,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92,24; 98,75</t>
+          <t>92,3; 98,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80,54; 90,77</t>
+          <t>80,26; 90,97</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,39; 98,51</t>
+          <t>90,16; 98,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,15; 91,93</t>
+          <t>78,23; 91,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,32; 95,17</t>
+          <t>82,93; 94,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,63; 80,19</t>
+          <t>61,53; 81,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,9; 98,93</t>
+          <t>90,91; 98,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,46; 94,34</t>
+          <t>81,94; 94,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,63; 91,87</t>
+          <t>78,42; 92,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>70,39; 90,19</t>
+          <t>70,35; 90,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,73; 97,83</t>
+          <t>92,44; 97,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82,18; 91,58</t>
+          <t>83,32; 92,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83,98; 92,59</t>
+          <t>83,15; 92,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,26; 83,95</t>
+          <t>70,15; 84,57</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,45; 90,79</t>
+          <t>69,85; 90,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>74,03; 94,28</t>
+          <t>75,89; 94,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,52; 95,13</t>
+          <t>78,6; 94,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,98; 97,63</t>
+          <t>85,46; 97,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,11; 90,7</t>
+          <t>69,73; 89,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,56; 94,93</t>
+          <t>78,04; 95,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,08; 88,32</t>
+          <t>68,38; 87,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,16; 97,28</t>
+          <t>83,63; 97,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>74,38; 88,64</t>
+          <t>75,23; 88,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79,71; 92,55</t>
+          <t>80,12; 93,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76,59; 89,94</t>
+          <t>77,6; 89,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,04; 96,31</t>
+          <t>88,29; 96,48</t>
         </is>
       </c>
     </row>
@@ -1417,32 +1417,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>87,29; 97,64</t>
+          <t>86,98; 97,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,51; 97,52</t>
+          <t>85,72; 97,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84,84; 98,48</t>
+          <t>84,78; 98,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81,59; 95,8</t>
+          <t>81,49; 95,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92,61; 100,0</t>
+          <t>92,46; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,25; 90,91</t>
+          <t>73,29; 91,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89,96; 98,97</t>
+          <t>89,24; 98,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>92,12; 98,29</t>
+          <t>92,18; 98,29</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81,74; 93,22</t>
+          <t>81,6; 92,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91,93; 99,27</t>
+          <t>92,27; 99,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>88,58; 96,69</t>
+          <t>88,5; 96,72</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>83,86; 93,17</t>
+          <t>84,48; 93,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,79; 95,58</t>
+          <t>87,16; 95,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91,51; 97,91</t>
+          <t>91,83; 97,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79,34; 89,88</t>
+          <t>78,74; 89,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,73; 93,54</t>
+          <t>84,99; 93,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,96; 97,5</t>
+          <t>89,76; 97,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,28; 96,55</t>
+          <t>88,85; 96,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>74,67; 87,2</t>
+          <t>75,05; 87,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85,82; 92,31</t>
+          <t>85,56; 92,36</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89,92; 95,66</t>
+          <t>90,21; 95,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91,55; 96,31</t>
+          <t>91,68; 96,48</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,31; 87,15</t>
+          <t>78,71; 87,14</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>79,2; 88,72</t>
+          <t>79,08; 88,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,09; 94,37</t>
+          <t>87,06; 94,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83,14; 91,42</t>
+          <t>82,67; 91,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87,17; 95,21</t>
+          <t>87,59; 95,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>78,13; 87,72</t>
+          <t>77,64; 87,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>88,0; 94,75</t>
+          <t>87,64; 94,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,2; 92,15</t>
+          <t>84,4; 92,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>93,4; 98,54</t>
+          <t>93,55; 98,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>80,35; 87,31</t>
+          <t>80,42; 87,07</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88,64; 93,57</t>
+          <t>88,75; 93,65</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84,42; 90,92</t>
+          <t>84,97; 90,94</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>91,91; 96,4</t>
+          <t>91,86; 96,44</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>86,87; 90,63</t>
+          <t>86,62; 90,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>88,19; 92,12</t>
+          <t>88,22; 92,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91,45; 94,74</t>
+          <t>91,5; 94,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85,5; 90,07</t>
+          <t>85,57; 90,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>86,73; 90,52</t>
+          <t>86,82; 90,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>88,92; 92,59</t>
+          <t>88,93; 92,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89,16; 92,88</t>
+          <t>89,27; 92,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>85,44; 90,15</t>
+          <t>85,44; 90,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>87,41; 90,12</t>
+          <t>87,33; 90,05</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>89,17; 91,91</t>
+          <t>89,25; 91,84</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>90,94; 93,48</t>
+          <t>90,8; 93,29</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>86,17; 89,43</t>
+          <t>86,4; 89,63</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39281; 45677</t>
+          <t>39312; 45272</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42680; 51333</t>
+          <t>42489; 51461</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2224,47 +2224,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67212; 72370</t>
+          <t>68192; 72416</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42219; 49730</t>
+          <t>42511; 49787</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48140; 55968</t>
+          <t>47959; 55785</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54144; 60408</t>
+          <t>53463; 60411</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>71509; 76432</t>
+          <t>71321; 76427</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>84178; 94192</t>
+          <t>84533; 94156</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94769; 105604</t>
+          <t>94724; 105567</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>109363; 115908</t>
+          <t>109776; 115910</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>141465; 148030</t>
+          <t>141079; 148131</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72038; 83488</t>
+          <t>71761; 83360</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79774; 89990</t>
+          <t>80185; 90206</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90293; 96135</t>
+          <t>89436; 95919</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99971; 117083</t>
+          <t>100585; 118422</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80550; 92841</t>
+          <t>80255; 92754</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81036; 93220</t>
+          <t>81535; 92683</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87136; 98364</t>
+          <t>86807; 98279</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89209; 107628</t>
+          <t>88762; 107508</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>156070; 172961</t>
+          <t>156076; 172645</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>165660; 179854</t>
+          <t>165762; 180997</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>180900; 193104</t>
+          <t>180630; 192758</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>196019; 222938</t>
+          <t>193745; 222656</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57797; 62612</t>
+          <t>57790; 62611</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53725; 60840</t>
+          <t>53365; 60674</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54652; 60352</t>
+          <t>54588; 60375</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44453; 53052</t>
+          <t>44941; 53103</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>59120; 64022</t>
+          <t>58950; 64022</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60297; 65777</t>
+          <t>60889; 65784</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59224; 65226</t>
+          <t>59858; 65228</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50302; 60298</t>
+          <t>49239; 60099</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>119209; 125984</t>
+          <t>119044; 126053</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117484; 125625</t>
+          <t>117097; 125822</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117207; 125480</t>
+          <t>117288; 125481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>98539; 111067</t>
+          <t>98208; 111308</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63867; 69608</t>
+          <t>63710; 69594</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57350; 66608</t>
+          <t>56683; 66596</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60623; 69246</t>
+          <t>60339; 68997</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42945; 55880</t>
+          <t>42872; 56651</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69405; 75539</t>
+          <t>69416; 75548</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64019; 73242</t>
+          <t>63620; 73205</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60637; 70847</t>
+          <t>60477; 71252</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53049; 67972</t>
+          <t>53024; 67968</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>136327; 143822</t>
+          <t>135893; 143803</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>123344; 137451</t>
+          <t>125063; 138489</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125862; 138768</t>
+          <t>124627; 138135</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>100455; 121764</t>
+          <t>101747; 122671</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27126; 34960</t>
+          <t>26894; 35035</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30460; 38792</t>
+          <t>31225; 38773</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31752; 38963</t>
+          <t>32192; 38908</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29404; 33389</t>
+          <t>29229; 33394</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>29918; 38161</t>
+          <t>29338; 37845</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35997; 42947</t>
+          <t>35309; 43071</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28989; 37607</t>
+          <t>29117; 37452</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34269; 39611</t>
+          <t>34052; 39576</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59937; 71422</t>
+          <t>60616; 71694</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68865; 79953</t>
+          <t>69220; 80564</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63986; 75131</t>
+          <t>64827; 75040</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65957; 72151</t>
+          <t>66145; 72284</t>
         </is>
       </c>
     </row>
@@ -3249,32 +3249,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46611; 52135</t>
+          <t>46445; 52119</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41961; 47857</t>
+          <t>42068; 47868</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42785; 49662</t>
+          <t>42751; 49643</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35830; 42067</t>
+          <t>35783; 42058</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>52892; 57110</t>
+          <t>52801; 57110</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40746; 50568</t>
+          <t>40766; 50664</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>48723; 53603</t>
+          <t>48333; 53594</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>101799; 108616</t>
+          <t>101861; 108612</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>85576; 97600</t>
+          <t>85433; 97112</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>95934; 103594</t>
+          <t>96289; 103606</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>86872; 94830</t>
+          <t>86791; 94857</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>102725; 114131</t>
+          <t>103481; 114198</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>110692; 121902</t>
+          <t>111161; 122128</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118808; 127129</t>
+          <t>119226; 127083</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>98053; 111072</t>
+          <t>97301; 110695</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>106546; 117625</t>
+          <t>106871; 117573</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>117471; 127315</t>
+          <t>117201; 126897</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>119453; 129174</t>
+          <t>118879; 129130</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>115625; 135035</t>
+          <t>116217; 134818</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>213032; 229139</t>
+          <t>212381; 229264</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>232092; 246905</t>
+          <t>232835; 246809</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>241347; 253897</t>
+          <t>241700; 254363</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>218035; 242652</t>
+          <t>219156; 242637</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>116509; 130515</t>
+          <t>116325; 130450</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>136627; 148055</t>
+          <t>136572; 147876</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>123815; 136145</t>
+          <t>123121; 136246</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>113214; 123662</t>
+          <t>113763; 123911</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>120550; 135349</t>
+          <t>119805; 135591</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>144923; 156036</t>
+          <t>144333; 156057</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>133708; 146333</t>
+          <t>134030; 147023</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>144219; 152160</t>
+          <t>144449; 152192</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>242173; 263146</t>
+          <t>242400; 262432</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>285026; 300888</t>
+          <t>285388; 301148</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>259796; 279781</t>
+          <t>261461; 279848</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>261288; 274067</t>
+          <t>261151; 274178</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>552531; 576424</t>
+          <t>550920; 577113</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>582311; 608271</t>
+          <t>582533; 607939</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>600248; 621850</t>
+          <t>600600; 621485</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>561306; 591304</t>
+          <t>561769; 591434</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>588262; 613949</t>
+          <t>588853; 615466</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>622104; 647771</t>
+          <t>622114; 647513</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>622476; 648463</t>
+          <t>623220; 648223</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>638014; 673197</t>
+          <t>638033; 672062</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1148769; 1184449</t>
+          <t>1147811; 1183551</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1212613; 1249917</t>
+          <t>1213770; 1248925</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1231855; 1266165</t>
+          <t>1229970; 1263683</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1209241; 1254989</t>
+          <t>1212458; 1257706</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2005-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89,17%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>90,05%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>95,9%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>91,9%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>88,18%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>89,17%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>90,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>95,9%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,62; 96,3</t>
+          <t>80,18; 94,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,04; 94,52</t>
+          <t>82,33; 95,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>88,17; 99,02</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>92,38; 99,25</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,78; 97,15</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,14; 94,15</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>93,59; 99,39</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>80,95; 94,81</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>81,62; 94,94</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,64; 99,03</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>92,61; 99,24</t>
+          <t>91,57; 99,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84,94; 94,61</t>
+          <t>84,73; 94,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83,68; 93,26</t>
+          <t>83,24; 93,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94,23; 99,49</t>
+          <t>93,87; 99,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,13; 98,84</t>
+          <t>93,91; 98,71</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>82,57%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>87,47%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89,26%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>79,04%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>83,61%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>89,63%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>97,08%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>86,93%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>82,57%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>87,47%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>89,26%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>81,38%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,67; 89,07</t>
+          <t>75,96; 88,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,55; 93,99</t>
+          <t>80,92; 91,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92,35; 99,05</t>
+          <t>82,85; 93,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80,08; 94,28</t>
+          <t>71,07; 86,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>76,06; 87,91</t>
+          <t>76,31; 88,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,01; 92,09</t>
+          <t>82,68; 93,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,69; 93,61</t>
+          <t>92,85; 99,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,2; 86,24</t>
+          <t>76,94; 89,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78,39; 86,71</t>
+          <t>78,25; 86,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84,3; 92,05</t>
+          <t>84,13; 91,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89,5; 95,51</t>
+          <t>89,59; 95,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,41; 88,96</t>
+          <t>76,12; 85,73</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>86,67%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>96,78%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>92,72%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>96,01%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>87,46%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>87,89%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>94,88%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>96,28%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>85,32%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91,32; 98,94</t>
+          <t>90,66; 99,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,98; 96,61</t>
+          <t>91,65; 99,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,31; 98,78</t>
+          <t>90,8; 98,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79,13; 93,51</t>
+          <t>79,14; 92,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,18; 99,02</t>
+          <t>92,39; 98,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,67; 99,04</t>
+          <t>85,57; 96,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,77; 98,91</t>
+          <t>89,52; 98,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75,1; 91,67</t>
+          <t>79,23; 93,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93,05; 98,53</t>
+          <t>93,41; 98,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90,62; 97,37</t>
+          <t>90,72; 97,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92,3; 98,75</t>
+          <t>92,37; 98,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80,26; 90,97</t>
+          <t>82,09; 91,38</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>96,2%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>89,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>86,52%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>81,01%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>95,52%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>86,22%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>90,35%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>72,37%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>96,2%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>89,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,52%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,16; 98,49</t>
+          <t>91,33; 99,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,23; 91,91</t>
+          <t>82,63; 94,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,93; 94,82</t>
+          <t>78,15; 92,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,53; 81,3</t>
+          <t>69,73; 89,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,91; 98,95</t>
+          <t>90,26; 97,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,94; 94,29</t>
+          <t>78,67; 92,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,42; 92,39</t>
+          <t>83,08; 95,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>70,35; 90,18</t>
+          <t>62,55; 80,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,44; 97,82</t>
+          <t>92,79; 97,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83,32; 92,27</t>
+          <t>83,45; 91,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83,15; 92,16</t>
+          <t>83,31; 92,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,15; 84,57</t>
+          <t>69,16; 84,08</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>82,65%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>89,03%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79,94%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>92,27%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>82,53%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>86,67%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>88,37%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>93,51%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>82,65%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>89,03%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>79,94%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>69,85; 90,99</t>
+          <t>72,11; 91,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75,89; 94,23</t>
+          <t>78,91; 95,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,6; 94,99</t>
+          <t>67,81; 88,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,46; 97,64</t>
+          <t>84,58; 97,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>69,73; 89,95</t>
+          <t>69,5; 90,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,04; 95,2</t>
+          <t>75,57; 94,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,38; 87,96</t>
+          <t>77,82; 95,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,63; 97,19</t>
+          <t>85,79; 97,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>75,23; 88,97</t>
+          <t>74,33; 88,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80,12; 93,26</t>
+          <t>80,97; 93,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77,6; 89,83</t>
+          <t>76,48; 89,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,29; 96,48</t>
+          <t>87,28; 96,49</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>83,67%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>96,2%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>93,75%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>93,54%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>93,52%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>90,14%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86,98; 97,61</t>
+          <t>92,35; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,72; 97,54</t>
+          <t>73,65; 90,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84,78; 98,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81,49; 95,78</t>
+          <t>89,64; 98,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92,46; 100,0</t>
+          <t>86,52; 97,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,29; 91,08</t>
+          <t>84,84; 98,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>83,75; 98,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89,24; 98,95</t>
+          <t>80,17; 95,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>92,18; 98,29</t>
+          <t>91,71; 98,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81,6; 92,75</t>
+          <t>82,42; 92,94</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92,27; 99,28</t>
+          <t>91,93; 99,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>88,5; 96,72</t>
+          <t>87,77; 96,74</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>89,78%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>80,93%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>89,08%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>92,03%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>95,34%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>84,93%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>89,78%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>94,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>93,56%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,54%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>84,48; 93,23</t>
+          <t>84,91; 93,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,16; 95,76</t>
+          <t>89,79; 97,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91,83; 97,88</t>
+          <t>89,05; 96,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78,74; 89,57</t>
+          <t>73,69; 86,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,99; 93,5</t>
+          <t>83,8; 93,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,76; 97,18</t>
+          <t>86,84; 95,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,85; 96,51</t>
+          <t>91,28; 97,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>75,05; 87,06</t>
+          <t>77,97; 89,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85,56; 92,36</t>
+          <t>85,82; 92,21</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90,21; 95,62</t>
+          <t>90,19; 95,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91,68; 96,48</t>
+          <t>91,75; 96,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,71; 87,14</t>
+          <t>77,77; 86,24</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>91,63%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>88,72%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>84,23%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>91,04%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>87,86%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>92,18%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>88,72%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>79,08; 88,68</t>
+          <t>77,85; 88,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,06; 94,26</t>
+          <t>87,79; 94,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82,67; 91,49</t>
+          <t>84,53; 92,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87,59; 95,41</t>
+          <t>94,02; 98,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>77,64; 87,88</t>
+          <t>79,37; 88,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,64; 94,76</t>
+          <t>86,6; 94,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,4; 92,58</t>
+          <t>83,42; 91,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>93,55; 98,56</t>
+          <t>87,85; 95,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>80,42; 87,07</t>
+          <t>80,33; 86,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88,75; 93,65</t>
+          <t>88,91; 93,75</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84,97; 90,94</t>
+          <t>85,35; 91,18</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>91,86; 96,44</t>
+          <t>92,15; 96,77</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>88,82%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>90,91%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>88,84%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>90,33%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>93,23%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>87,82%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>88,82%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>90,91%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>91,19%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>86,62; 90,74</t>
+          <t>86,69; 90,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>88,22; 92,07</t>
+          <t>88,86; 92,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91,5; 94,68</t>
+          <t>89,35; 92,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85,57; 90,09</t>
+          <t>85,52; 90,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>86,82; 90,74</t>
+          <t>86,8; 90,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>88,93; 92,56</t>
+          <t>88,31; 92,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89,27; 92,85</t>
+          <t>91,3; 94,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>85,44; 90,0</t>
+          <t>84,68; 89,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>87,33; 90,05</t>
+          <t>87,59; 90,24</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>89,25; 91,84</t>
+          <t>89,25; 91,75</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>90,8; 93,29</t>
+          <t>90,9; 93,33</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>86,4; 89,63</t>
+          <t>85,92; 88,99</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>92</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>46827</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52915</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>58497</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60308</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>43204</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>48010</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>55501</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>71009</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>46827</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>52915</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58497</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74770</t>
+          <t>54445</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>145778</t>
+          <t>114753</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39312; 45272</t>
+          <t>42108; 49638</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42489; 51461</t>
+          <t>48376; 56053</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>53783; 60405</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>57507; 61784</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>39859; 45671</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>42543; 51258</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>68192; 72416</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>42511; 49787</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>47959; 55785</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>53463; 60411</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>71321; 76427</t>
+          <t>51398; 55660</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>84533; 94156</t>
+          <t>84324; 94050</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94724; 105567</t>
+          <t>94227; 105392</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>109776; 115910</t>
+          <t>109361; 115921</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>141079; 148131</t>
+          <t>111172; 116855</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>115</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>87125</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88041</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>93713</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>78251</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>86023</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>94018</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>109199</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87125</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88041</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93713</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>99330</t>
+          <t>83627</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>208528</t>
+          <t>173390</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71761; 83360</t>
+          <t>80146; 92998</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80185; 90206</t>
+          <t>81443; 92470</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89436; 95919</t>
+          <t>86979; 98465</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100585; 118422</t>
+          <t>80719; 97772</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80255; 92754</t>
+          <t>71420; 83292</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81535; 92683</t>
+          <t>79349; 90095</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86807; 98279</t>
+          <t>89914; 96150</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>88762; 107508</t>
+          <t>76552; 89080</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>156076; 172645</t>
+          <t>155800; 172893</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>165762; 180997</t>
+          <t>165420; 180695</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>180630; 192758</t>
+          <t>180811; 192878</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>193745; 222656</t>
+          <t>162184; 182667</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>83</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>62248</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>64373</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>63657</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50330</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>61242</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>58230</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>58686</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>49671</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>62248</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>64373</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>63657</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>55939</t>
+          <t>48556</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>105610</t>
+          <t>98886</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57790; 62611</t>
+          <t>58613; 64039</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53365; 60674</t>
+          <t>60877; 65773</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54588; 60375</t>
+          <t>59878; 65231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44941; 53103</t>
+          <t>45955; 53609</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>58950; 64022</t>
+          <t>58464; 62611</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60889; 65784</t>
+          <t>53738; 60678</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59858; 65228</t>
+          <t>54715; 60367</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49239; 60099</t>
+          <t>43771; 51612</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>119044; 126053</t>
+          <t>119499; 126031</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117097; 125822</t>
+          <t>117225; 125914</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117288; 125481</t>
+          <t>117376; 125401</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>98208; 111308</t>
+          <t>93018; 103545</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>68</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>73455</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>69556</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66725</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>56555</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>67494</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>62468</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>65739</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>50431</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73455</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>69556</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>66725</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>61416</t>
+          <t>51257</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>111846</t>
+          <t>107812</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63710; 69594</t>
+          <t>69734; 75642</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56683; 66596</t>
+          <t>64153; 73178</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60339; 68997</t>
+          <t>60269; 71016</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42872; 56651</t>
+          <t>48680; 62278</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69416; 75548</t>
+          <t>63776; 69128</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63620; 73205</t>
+          <t>57000; 67214</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60477; 71252</t>
+          <t>60448; 69169</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53024; 67968</t>
+          <t>44073; 56876</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>135893; 143803</t>
+          <t>136407; 143948</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>125063; 138489</t>
+          <t>125254; 137942</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124627; 138135</t>
+          <t>124860; 138737</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>101747; 122671</t>
+          <t>97021; 117950</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34773</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>40280</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>34038</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>36520</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>31777</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>35661</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>36198</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>31980</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>34773</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>40280</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34038</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37639</t>
+          <t>33254</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69618</t>
+          <t>69774</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26894; 35035</t>
+          <t>30340; 38521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31225; 38773</t>
+          <t>35701; 43064</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32192; 38908</t>
+          <t>28875; 37593</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29229; 33394</t>
+          <t>33476; 38412</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>29338; 37845</t>
+          <t>26762; 34920</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35309; 43071</t>
+          <t>31096; 38791</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29117; 37452</t>
+          <t>31873; 38912</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34052; 39576</t>
+          <t>30343; 34647</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60616; 71694</t>
+          <t>59897; 71323</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69220; 80564</t>
+          <t>69949; 80422</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64827; 75040</t>
+          <t>63894; 74789</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>66145; 72284</t>
+          <t>65418; 72317</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>55873</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>46541</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>53925</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>45663</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>50060</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>45904</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>47160</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>39581</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>55873</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>46541</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>53925</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>52128</t>
+          <t>39643</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91709</t>
+          <t>85306</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46445; 52119</t>
+          <t>52744; 57110</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42068; 47868</t>
+          <t>40968; 50542</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42751; 49643</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35783; 42058</t>
+          <t>42552; 46980</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>52801; 57110</t>
+          <t>46198; 52070</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40766; 50664</t>
+          <t>41634; 48128</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>42232; 49652</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>48333; 53594</t>
+          <t>35498; 42320</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>101861; 108612</t>
+          <t>101347; 108520</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>85433; 97112</t>
+          <t>86294; 97303</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96289; 103606</t>
+          <t>95934; 103596</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>86791; 94857</t>
+          <t>80529; 88760</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>146</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>112895</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>123363</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>125172</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>113635</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>109111</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>117369</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>123784</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>104960</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>112895</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>123363</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>125172</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>126628</t>
+          <t>102323</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>231588</t>
+          <t>215957</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>103481; 114198</t>
+          <t>106766; 117610</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>111161; 122128</t>
+          <t>117244; 126880</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119226; 127083</t>
+          <t>119147; 129167</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>97301; 110695</t>
+          <t>103482; 121919</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>106871; 117573</t>
+          <t>102653; 113958</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>117201; 126897</t>
+          <t>110751; 121534</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>118879; 129130</t>
+          <t>118514; 127079</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>116217; 134818</t>
+          <t>94512; 108159</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>212381; 229264</t>
+          <t>213028; 228900</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>232835; 246809</t>
+          <t>232797; 246843</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>241700; 254363</t>
+          <t>241891; 254139</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>219156; 242637</t>
+          <t>203488; 225638</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>207</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>171</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>129248</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>150906</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>140884</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>152682</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>123903</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>142823</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>130851</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>119720</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>129248</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>150906</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>140884</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>149242</t>
+          <t>128482</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>268963</t>
+          <t>281165</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>116325; 130450</t>
+          <t>120122; 136069</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>136572; 147876</t>
+          <t>144567; 155607</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>123121; 136246</t>
+          <t>134230; 146879</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>113763; 123911</t>
+          <t>147987; 155625</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>119805; 135591</t>
+          <t>116753; 130638</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>144333; 156057</t>
+          <t>135864; 147558</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>134030; 147023</t>
+          <t>124237; 136609</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>144449; 152192</t>
+          <t>122088; 133215</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>242400; 262432</t>
+          <t>242125; 261899</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>285388; 301148</t>
+          <t>285888; 301476</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>261461; 279848</t>
+          <t>262640; 280578</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>261151; 274178</t>
+          <t>273097; 286798</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>842</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>861</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>918</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>804</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>829</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>602445</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>635974</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>636612</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>605456</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>565042</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>596489</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>611937</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>576551</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>602445</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>635974</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>636612</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>657092</t>
+          <t>541586</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1233643</t>
+          <t>1147041</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>550920; 577113</t>
+          <t>588001; 615775</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>582533; 607939</t>
+          <t>621627; 647096</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>600600; 621485</t>
+          <t>623795; 648383</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>561769; 591434</t>
+          <t>588897; 619965</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>588853; 615466</t>
+          <t>552078; 577011</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>622114; 647513</t>
+          <t>583154; 609046</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>623220; 648223</t>
+          <t>599300; 621013</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>638033; 672062</t>
+          <t>526008; 553879</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1147811; 1183551</t>
+          <t>1151246; 1186030</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1213770; 1248925</t>
+          <t>1213678; 1247739</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1229970; 1263683</t>
+          <t>1231256; 1264212</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1212458; 1257706</t>
+          <t>1125379; 1165551</t>
         </is>
       </c>
     </row>
